--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/antofagasta.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/antofagasta.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1153.22</v>
+        <v>1138.58</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>10478.35</v>
+        <v>10463.65</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>7396.24</v>
+        <v>7616.08</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>10411.98</v>
+        <v>10506.69</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>6889.71</v>
+        <v>6937.67</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>10550.55</v>
+        <v>10476.09</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3497.76</v>
+        <v>3497.58</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>808.46</v>
+        <v>808.42</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1491.93</v>
+        <v>1457.21</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1075.61</v>
+        <v>1050.58</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>22980.04</v>
+        <v>23545.58</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>11395.23</v>
+        <v>11524.82</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>5100.24</v>
+        <v>5157.28</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3654.43</v>
+        <v>3645.2</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>3196.47</v>
+        <v>3233.97</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>10625.62</v>
+        <v>10673.88</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>7727.71</v>
+        <v>7801.11</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>14711.1</v>
+        <v>14809.57</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/antofagasta.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1288419-60-CM25</t>
+          <t>2385-351-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.252.500-0</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gestión del Riesgo de Desastres</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1138.58</v>
+        <v>11725.07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3506-943-CM25</t>
+          <t>1288419-60-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>69.252.500-0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>Gestión del Riesgo de Desastres</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>10463.65</v>
+        <v>1138.58</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1079454-19-CM26</t>
+          <t>3506-943-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>7616.08</v>
+        <v>10463.65</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2430-28-CM26</t>
+          <t>1079454-19-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>SECCIÓN COMPRAS II ZONA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>10506.69</v>
+        <v>7616.08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1288419-7-CM26</t>
+          <t>2430-28-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,22 +773,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.252.500-0</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gestión del Riesgo de Desastres</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>6937.67</v>
+        <v>10506.69</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3506-151-CM26</t>
+          <t>1288419-7-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>69.252.500-0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>Gestión del Riesgo de Desastres</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>10476.09</v>
+        <v>6937.67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>778992-26-CM26</t>
+          <t>3506-151-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,22 +895,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3497.58</v>
+        <v>10476.09</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>778992-27-CM26</t>
+          <t>778992-26-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>808.42</v>
+        <v>3497.58</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2385-200-CM26</t>
+          <t>778992-27-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>Regimiento Reforzado N° 1 "Calama"</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1457.21</v>
+        <v>808.42</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2385-198-CM26</t>
+          <t>2385-200-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1050.58</v>
+        <v>1457.21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1079454-109-CM26</t>
+          <t>2385-198-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>23545.58</v>
+        <v>1050.58</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2429-375-CM26</t>
+          <t>1079454-109-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,22 +1200,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>SECCIÓN COMPRAS II ZONA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>11524.82</v>
+        <v>23545.58</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1079454-153-CM26</t>
+          <t>2429-375-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,27 +1256,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>5157.28</v>
+        <v>11524.82</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3506-339-CM26</t>
+          <t>1079454-153-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>SECCIÓN COMPRAS II ZONA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3645.2</v>
+        <v>5157.28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>778992-156-CM26</t>
+          <t>3506-339-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,27 +1378,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>3233.97</v>
+        <v>3645.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3506-436-CM26</t>
+          <t>778992-156-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,22 +1444,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>Regimiento Reforzado N° 1 "Calama"</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>10673.88</v>
+        <v>3233.97</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1079454-280-CM26</t>
+          <t>3506-436-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>7801.11</v>
+        <v>10673.88</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3149-231-CM26</t>
+          <t>1079454-280-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.253.600-2</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+          <t>SECCIÓN COMPRAS II ZONA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,6 +1606,67 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
+        <v>7801.11</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3149-231-CM26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>69.253.600-2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
         <v>14809.57</v>
       </c>
     </row>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/antofagasta.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/antofagasta.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Antofagasta" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Antofagasta" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2385-351-CM25</t>
+          <t>3506-38-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>11725.07</v>
+        <v>9482.32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1288419-60-CM25</t>
+          <t>4051-18-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.252.500-0</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gestión del Riesgo de Desastres</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>RASTRO RETAIL SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.888.564-6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1138.58</v>
+        <v>639.22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3506-943-CM25</t>
+          <t>4051-19-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>COMERCIALIZADORA EXPRESSVIRTUAL SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.511.768-2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>10463.65</v>
+        <v>3363.16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1079454-19-CM26</t>
+          <t>3506-158-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>7616.08</v>
+        <v>10193.54</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2430-28-CM26</t>
+          <t>778992-75-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>10506.69</v>
+        <v>3131.68</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1288419-7-CM26</t>
+          <t>778992-76-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.252.500-0</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gestión del Riesgo de Desastres</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>6937.67</v>
+        <v>2911.14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3506-151-CM26</t>
+          <t>778989-63-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>65.081.190-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SURTI VENTAS S.A.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.462.500-5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>10476.09</v>
+        <v>12242.56</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>778992-26-CM26</t>
+          <t>2385-351-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3497.58</v>
+        <v>11725.07</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>778992-27-CM26</t>
+          <t>778992-183-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>808.42</v>
+        <v>9751.209999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2385-200-CM26</t>
+          <t>3506-443-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1457.21</v>
+        <v>10264.94</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2385-198-CM26</t>
+          <t>3834-179-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1050.58</v>
+        <v>3744.23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1079454-109-CM26</t>
+          <t>3834-176-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,27 +1195,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>23545.58</v>
+        <v>9847.559999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2429-375-CM26</t>
+          <t>3834-177-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>FIRAMCO SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.942.697-1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>11524.82</v>
+        <v>2860.84</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1079454-153-CM26</t>
+          <t>3506-606-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>5157.28</v>
+        <v>11562.45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3506-339-CM26</t>
+          <t>3834-202-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,27 +1378,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>3645.2</v>
+        <v>610.55</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>778992-156-CM26</t>
+          <t>778992-282-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3233.97</v>
+        <v>6098.42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3506-436-CM26</t>
+          <t>3834-210-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,27 +1500,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>10673.88</v>
+        <v>1990.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1079454-280-CM26</t>
+          <t>2385-997-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,27 +1561,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>7801.11</v>
+        <v>48664.67</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3149-231-CM26</t>
+          <t>1288419-60-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.253.600-2</t>
+          <t>69.252.500-0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+          <t>Gestión del Riesgo de Desastres</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,7 +1667,1105 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
+        <v>1138.58</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>3506-943-CM25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>69.020.100-3</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>10463.65</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1079454-19-CM26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>61.978.660-2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS II ZONA</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>7616.08</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2430-28-CM26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>10506.69</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1288419-7-CM26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>69.252.500-0</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Gestión del Riesgo de Desastres</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>6937.67</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3506-151-CM26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>69.020.100-3</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>10476.09</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>778992-26-CM26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>61.953.000-4</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Regimiento Reforzado N° 1 "Calama"</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>76.730.550-8</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>3497.58</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>778992-27-CM26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>61.953.000-4</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Regimiento Reforzado N° 1 "Calama"</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>76.730.550-8</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>808.42</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2385-200-CM26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>1457.21</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2385-198-CM26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>1050.58</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1079454-109-CM26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>61.978.660-2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS II ZONA</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>23545.58</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2429-375-CM26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>11524.82</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1079454-153-CM26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>61.978.660-2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS II ZONA</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>SODIMAC S.A.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>96.792.430-K</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>5157.28</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>3506-339-CM26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>69.020.100-3</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>3645.2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>778992-156-CM26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>61.953.000-4</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Regimiento Reforzado N° 1 "Calama"</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>76.730.550-8</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>3233.97</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>3506-436-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>69.020.100-3</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>10673.88</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1079454-280-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>61.978.660-2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS II ZONA</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>SODIMAC S.A.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>96.792.430-K</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>7801.11</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>3149-231-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>69.253.600-2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
         <v>14809.57</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>3149-252-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>69.253.600-2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>32772.92</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/antofagasta.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -758,7 +758,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>778992-75-CM25</t>
+          <t>778992-76-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3131.68</v>
+        <v>2911.14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>778992-76-CM25</t>
+          <t>778992-75-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2911.14</v>
+        <v>3131.68</v>
       </c>
     </row>
     <row r="8">
@@ -1124,7 +1124,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3834-179-CM25</t>
+          <t>3834-176-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3744.23</v>
+        <v>9847.559999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3834-176-CM25</t>
+          <t>3834-177-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>FIRAMCO SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.942.697-1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>9847.559999999999</v>
+        <v>2860.84</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3834-177-CM25</t>
+          <t>3834-179-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>FIRAMCO SPA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.942.697-1</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>2860.84</v>
+        <v>3744.23</v>
       </c>
     </row>
     <row r="15">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gestión del Riesgo de Desastres</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gestión del Riesgo de Desastres</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2100,7 +2100,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2385-200-CM26</t>
+          <t>2385-198-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1457.21</v>
+        <v>1050.58</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2385-198-CM26</t>
+          <t>2385-200-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1050.58</v>
+        <v>1457.21</v>
       </c>
     </row>
     <row r="30">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2766,6 +2766,311 @@
       </c>
       <c r="M38" s="2" t="n">
         <v>32772.92</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1288419-49-CM26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>69.252.500-0</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>SODIMAC S.A.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>96.792.430-K</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>6983.58</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1288419-50-CM26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>69.252.500-0</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>7583.92</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>3506-692-CM26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>69.020.100-3</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>12095.26</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>4051-185-CM26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>69.252.600-7</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>5584.37</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>778989-167-CM26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>65.081.190-9</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA Y COMERCIALIZADORA SANTA ELIANA SPA</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>77.544.929-2</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>2632.39</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/antofagasta.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/antofagasta.xlsx
@@ -562,7 +562,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>77.888.564-6</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1001,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1127,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1192,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1257,11 @@
           <t>77.942.697-1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1322,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1387,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1452,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1517,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1582,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1647,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1712,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1777,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1842,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1907,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1972,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2037,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2224,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2289,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2354,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2419,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2545,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2671,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2797,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2862,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3049,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3114,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3179,11 @@
           <t>77.544.929-2</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/antofagasta.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2879,7 +2879,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1288419-49-CM26</t>
+          <t>1288419-50-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2934,13 +2934,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>6983.58</v>
+        <v>7583.92</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1288419-50-CM26</t>
+          <t>1288419-49-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2980,12 +2980,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>7583.92</v>
+        <v>6983.58</v>
       </c>
     </row>
     <row r="41">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3191,6 +3191,132 @@
       </c>
       <c r="M43" s="2" t="n">
         <v>2632.39</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>778998-149-CM26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>61.964.800-5</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>1087.83</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2605-91-CM26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>1444.99</v>
       </c>
     </row>
   </sheetData>
